--- a/Result/profitability/1904.xlsx
+++ b/Result/profitability/1904.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.12</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1975</v>
+        <v>0.3025</v>
       </c>
       <c r="N2" t="n">
-        <v>17.0425</v>
+        <v>17.93625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.34</v>
       </c>
       <c r="M3" t="n">
-        <v>0.23375</v>
+        <v>0.33125</v>
       </c>
       <c r="N3" t="n">
-        <v>17.56625</v>
+        <v>18.1425</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.2</v>
       </c>
       <c r="M4" t="n">
-        <v>0.245</v>
+        <v>0.34625</v>
       </c>
       <c r="N4" t="n">
-        <v>17.8475</v>
+        <v>18.4275</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.57</v>
       </c>
       <c r="M5" t="n">
-        <v>0.16375</v>
+        <v>0.28125</v>
       </c>
       <c r="N5" t="n">
-        <v>16.32875</v>
+        <v>16.675</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         <v>0.25</v>
       </c>
       <c r="M6" t="n">
-        <v>0.20125</v>
+        <v>0.295</v>
       </c>
       <c r="N6" t="n">
-        <v>16.6175</v>
+        <v>17.055</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.23</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2125</v>
+        <v>0.2525000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>17.07875</v>
+        <v>17.02125</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1279,7 +1279,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.32</v>
       </c>
       <c r="M8" t="n">
-        <v>0.18125</v>
+        <v>0.2225</v>
       </c>
       <c r="N8" t="n">
-        <v>17.12375</v>
+        <v>17.11</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1904</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>11685</v>
+      </c>
+      <c r="D75" t="n">
+        <v>9287</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2398</v>
+      </c>
+      <c r="F75" t="n">
+        <v>20.52</v>
+      </c>
+      <c r="G75" t="n">
+        <v>847</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>7.25%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>554</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1401</v>
+      </c>
+      <c r="K75" t="n">
+        <v>985</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.29375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>17.7575</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.5892857142857142</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.1099999999999994</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.005332040717401787</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-18.8</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.156056338028169</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
